--- a/tests/DataValidation/GC/TC08_CRDCDH-686_VerifyInvalidIntegerValue.xlsx
+++ b/tests/DataValidation/GC/TC08_CRDCDH-686_VerifyInvalidIntegerValue.xlsx
@@ -496,7 +496,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>verify_validation_results_for_tc</t>
+          <t>verify_validation_results</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
